--- a/output/pdf_financials_xlsx/CUPR.xlsx
+++ b/output/pdf_financials_xlsx/CUPR.xlsx
@@ -1923,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.062478</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.516481</v>
       </c>
     </row>
     <row r="93">
@@ -3071,7 +3071,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3292,7 +3296,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CUPR.xlsx
+++ b/output/pdf_financials_xlsx/CUPR.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005558</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007463</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.532449</v>
+        <v>-0.538007</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.330317</v>
+        <v>-2.33778</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.969246</v>
+        <v>-4.969263</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.532449</v>
+        <v>-0.538007</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.330317</v>
+        <v>-2.33778</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.969246</v>
+        <v>-4.969263</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.055947</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.169515</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001881</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.055947</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.169515</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001881</v>
       </c>
     </row>
     <row r="37">
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.345474</v>
+        <v>0.175959</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.250052</v>
+        <v>0.248171</v>
       </c>
     </row>
     <row r="49">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">

--- a/output/pdf_financials_xlsx/CUPR.xlsx
+++ b/output/pdf_financials_xlsx/CUPR.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.361088</v>
+        <v>0.362346</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.380928</v>
+        <v>0.441474</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.274232</v>
+        <v>1.39402</v>
       </c>
     </row>
     <row r="8">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.361088</v>
+        <v>0.362346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.380928</v>
+        <v>0.441474</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.274232</v>
+        <v>1.39402</v>
       </c>
     </row>
     <row r="11">
@@ -4615,7 +4615,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.001258</v>
       </c>
